--- a/excel_model/pricing_roi_model.xlsx
+++ b/excel_model/pricing_roi_model.xlsx
@@ -460,7 +460,7 @@
         <v>0.2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.004514839704040504</v>
+        <v>0.9637334551074038</v>
       </c>
       <c r="E8">
         <f>B8*(1-C8)*(D8/100)</f>
@@ -492,7 +492,7 @@
         <v>0.2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4908885850676371</v>
+        <v>0.5426749272451911</v>
       </c>
       <c r="E9">
         <f>B9*(1-C9)*(D9/100)</f>
@@ -524,7 +524,7 @@
         <v>0.2</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2344065315061108</v>
+        <v>0.2243642244016889</v>
       </c>
       <c r="E10">
         <f>B10*(1-C10)*(D10/100)</f>
@@ -556,7 +556,7 @@
         <v>0.2</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8508419620279671</v>
+        <v>0.8252208564099481</v>
       </c>
       <c r="E11">
         <f>B11*(1-C11)*(D11/100)</f>
@@ -588,7 +588,7 @@
         <v>0.2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2427971745705372</v>
+        <v>0.2637655254504525</v>
       </c>
       <c r="E12">
         <f>B12*(1-C12)*(D12/100)</f>
@@ -620,7 +620,7 @@
         <v>0.2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1060040676327117</v>
+        <v>0.1007640656243802</v>
       </c>
       <c r="E13">
         <f>B13*(1-C13)*(D13/100)</f>
@@ -652,7 +652,7 @@
         <v>0.2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2255390052511907</v>
+        <v>0.2575663674049251</v>
       </c>
       <c r="E14">
         <f>B14*(1-C14)*(D14/100)</f>
@@ -684,7 +684,7 @@
         <v>0.2</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1219629441340249</v>
+        <v>-0.01881152077455759</v>
       </c>
       <c r="E15">
         <f>B15*(1-C15)*(D15/100)</f>

--- a/excel_model/pricing_roi_model.xlsx
+++ b/excel_model/pricing_roi_model.xlsx
@@ -460,7 +460,7 @@
         <v>0.2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9637334551074038</v>
+        <v>0.6731930126607369</v>
       </c>
       <c r="E8">
         <f>B8*(1-C8)*(D8/100)</f>
@@ -492,7 +492,7 @@
         <v>0.2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5426749272451911</v>
+        <v>0.9471236479852601</v>
       </c>
       <c r="E9">
         <f>B9*(1-C9)*(D9/100)</f>
@@ -524,7 +524,7 @@
         <v>0.2</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2243642244016889</v>
+        <v>0.1980257567894181</v>
       </c>
       <c r="E10">
         <f>B10*(1-C10)*(D10/100)</f>
@@ -556,7 +556,7 @@
         <v>0.2</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8252208564099481</v>
+        <v>1.415381738121386</v>
       </c>
       <c r="E11">
         <f>B11*(1-C11)*(D11/100)</f>
@@ -588,7 +588,7 @@
         <v>0.2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2637655254504525</v>
+        <v>0.3340782809854737</v>
       </c>
       <c r="E12">
         <f>B12*(1-C12)*(D12/100)</f>
@@ -620,7 +620,7 @@
         <v>0.2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1007640656243802</v>
+        <v>0.09971596875792244</v>
       </c>
       <c r="E13">
         <f>B13*(1-C13)*(D13/100)</f>
@@ -652,7 +652,7 @@
         <v>0.2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2575663674049251</v>
+        <v>0.2841545882319225</v>
       </c>
       <c r="E14">
         <f>B14*(1-C14)*(D14/100)</f>
@@ -684,7 +684,7 @@
         <v>0.2</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.01881152077455759</v>
+        <v>0.03919736003879951</v>
       </c>
       <c r="E15">
         <f>B15*(1-C15)*(D15/100)</f>
